--- a/data/trans_orig/P41E_2023_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P41E_2023_R-Edad-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que en el último año sus relaciones sexuales han sido satisfactorias para ambas partes en 2023</t>
+          <t>Población que en el último año sus relaciones sexuales han sido satisfactorias para ambas partes en 2023 (tasa de respuesta: 69,32%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1804</t>
+          <t>1798</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16704</t>
+          <t>17241</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2734</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15579</t>
+          <t>15943</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6853</t>
+          <t>6542</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>26637</t>
+          <t>26370</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,72%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>82750</t>
+          <t>82213</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>97650</t>
+          <t>97656</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,2%</t>
+          <t>82,66%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>64163</t>
+          <t>63799</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>77008</t>
+          <t>77437</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>80,46%</t>
+          <t>80,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>152559</t>
+          <t>152826</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>172343</t>
+          <t>172654</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,14%</t>
+          <t>85,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,35%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1217</t>
+          <t>1211</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11478</t>
+          <t>12753</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1092</t>
+          <t>1177</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10415</t>
+          <t>10323</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3335</t>
+          <t>3580</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15870</t>
+          <t>15808</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,03%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>180527</t>
+          <t>179252</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>190788</t>
+          <t>190794</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>190122</t>
+          <t>190214</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>199445</t>
+          <t>199360</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>376672</t>
+          <t>376734</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>389207</t>
+          <t>388962</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,09%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3093</t>
+          <t>3334</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12121</t>
+          <t>13195</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3070</t>
+          <t>3179</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11583</t>
+          <t>12200</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7948</t>
+          <t>8342</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20413</t>
+          <t>21565</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,79%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>277849</t>
+          <t>276775</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>286877</t>
+          <t>286636</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>268014</t>
+          <t>267397</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>276527</t>
+          <t>276418</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>549154</t>
+          <t>548002</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>561619</t>
+          <t>561225</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,54%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3826</t>
+          <t>4334</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>34000</t>
+          <t>33907</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16494</t>
+          <t>16916</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>32004</t>
+          <t>31246</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>17690</t>
+          <t>17695</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>58576</t>
+          <t>59479</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,52%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>519163</t>
+          <t>519256</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>549337</t>
+          <t>548829</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>327671</t>
+          <t>328429</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>343181</t>
+          <t>342759</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>91,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>854262</t>
+          <t>853359</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>895148</t>
+          <t>895143</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>37489</t>
+          <t>37993</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>60416</t>
+          <t>60780</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>40537</t>
+          <t>40594</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>59462</t>
+          <t>58659</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>83510</t>
+          <t>84468</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>113899</t>
+          <t>113283</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>18,91%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>255712</t>
+          <t>255348</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>278639</t>
+          <t>278135</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>80,89%</t>
+          <t>80,77%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>88,14%</t>
+          <t>87,98%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>223629</t>
+          <t>224432</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>242554</t>
+          <t>242497</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>79,0%</t>
+          <t>79,28%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,68%</t>
+          <t>85,66%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>485320</t>
+          <t>485936</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>515709</t>
+          <t>514751</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>80,99%</t>
+          <t>81,09%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>85,9%</t>
         </is>
       </c>
     </row>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>40635</t>
+          <t>41444</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>61396</t>
+          <t>60587</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>31,07%</t>
+          <t>30,66%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>12696</t>
+          <t>11467</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>111956</t>
+          <t>113107</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>31,85%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>37427</t>
+          <t>37277</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>157582</t>
+          <t>157324</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>28,46%</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>136232</t>
+          <t>137041</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>156993</t>
+          <t>156184</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>68,93%</t>
+          <t>69,34%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>79,44%</t>
+          <t>79,03%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>243225</t>
+          <t>242074</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>342485</t>
+          <t>343714</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>68,48%</t>
+          <t>68,15%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>395227</t>
+          <t>395485</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>515382</t>
+          <t>515532</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>71,49%</t>
+          <t>71,54%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>93,26%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>34227</t>
+          <t>34008</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>49312</t>
+          <t>49589</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>31,03%</t>
+          <t>30,83%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>44,7%</t>
+          <t>44,95%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>40954</t>
+          <t>40738</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>54551</t>
+          <t>55233</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>37,41%</t>
+          <t>37,21%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>49,83%</t>
+          <t>50,45%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>77922</t>
+          <t>79336</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>99250</t>
+          <t>100176</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>36,1%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>45,16%</t>
+          <t>45,58%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>61000</t>
+          <t>60723</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>76085</t>
+          <t>76304</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>55,3%</t>
+          <t>55,05%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>68,97%</t>
+          <t>69,17%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>54934</t>
+          <t>54252</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>68531</t>
+          <t>68747</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>50,17%</t>
+          <t>49,55%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>62,59%</t>
+          <t>62,79%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>120547</t>
+          <t>119621</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>141875</t>
+          <t>140461</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>54,84%</t>
+          <t>54,42%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>64,55%</t>
+          <t>63,9%</t>
         </is>
       </c>
     </row>
@@ -3131,12 +3131,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>102485</t>
+          <t>111245</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>209182</t>
+          <t>214306</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3146,12 +3146,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>120512</t>
+          <t>115136</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>216301</t>
+          <t>216997</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3181,12 +3181,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>271699</t>
+          <t>259713</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>413790</t>
+          <t>414366</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,09%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1549479</t>
+          <t>1544355</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1656176</t>
+          <t>1647416</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>88,11%</t>
+          <t>87,81%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1451005</t>
+          <t>1450309</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1546794</t>
+          <t>1552170</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>87,03%</t>
+          <t>86,99%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3012177</t>
+          <t>3011601</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3154268</t>
+          <t>3166254</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>87,92%</t>
+          <t>87,91%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>92,42%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P41E_2023_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P41E_2023_R-Edad-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>7117</t>
+          <t>6068</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1798</t>
+          <t>1631</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17241</t>
+          <t>14710</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>7216</t>
+          <t>7637</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2305</t>
+          <t>2438</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15943</t>
+          <t>16978</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>14333</t>
+          <t>13704</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6542</t>
+          <t>6150</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>26370</t>
+          <t>24051</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>12,99%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>92337</t>
+          <t>91667</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>82213</t>
+          <t>83025</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>97656</t>
+          <t>96104</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,66%</t>
+          <t>84,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>72526</t>
+          <t>79752</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>63799</t>
+          <t>70411</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>77437</t>
+          <t>84951</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>91,26%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>80,01%</t>
+          <t>80,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>164863</t>
+          <t>171419</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>152826</t>
+          <t>161072</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>172654</t>
+          <t>178973</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>92,6%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,28%</t>
+          <t>87,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,68%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>99454</t>
+          <t>97735</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>99454</t>
+          <t>97735</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>99454</t>
+          <t>97735</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>79742</t>
+          <t>87389</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>79742</t>
+          <t>87389</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>79742</t>
+          <t>87389</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>179196</t>
+          <t>185123</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>179196</t>
+          <t>185123</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>179196</t>
+          <t>185123</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4091</t>
+          <t>4262</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1211</t>
+          <t>1255</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12753</t>
+          <t>10875</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4148</t>
+          <t>3887</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1177</t>
+          <t>949</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10323</t>
+          <t>8933</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>8238</t>
+          <t>8148</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3580</t>
+          <t>3524</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15808</t>
+          <t>16905</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,82%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>187914</t>
+          <t>212463</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>179252</t>
+          <t>205850</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>190794</t>
+          <t>215470</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>196389</t>
+          <t>222069</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>190214</t>
+          <t>217023</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>199360</t>
+          <t>225007</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>384304</t>
+          <t>434533</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>376734</t>
+          <t>425776</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>388962</t>
+          <t>439157</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,2%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>192005</t>
+          <t>216725</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>192005</t>
+          <t>216725</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>192005</t>
+          <t>216725</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>200537</t>
+          <t>225956</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>200537</t>
+          <t>225956</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>200537</t>
+          <t>225956</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>392542</t>
+          <t>442681</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>392542</t>
+          <t>442681</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>392542</t>
+          <t>442681</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,22 +1411,22 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>6732</t>
+          <t>7859</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3334</t>
+          <t>3849</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13195</t>
+          <t>14817</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>6433</t>
+          <t>6715</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3179</t>
+          <t>3191</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12200</t>
+          <t>12655</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>13165</t>
+          <t>14574</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8342</t>
+          <t>9150</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>21565</t>
+          <t>23123</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,54%</t>
         </is>
       </c>
     </row>
@@ -1524,27 +1524,27 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>283238</t>
+          <t>325946</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>276775</t>
+          <t>318988</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>286636</t>
+          <t>329956</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>273164</t>
+          <t>312296</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>267397</t>
+          <t>306356</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>276418</t>
+          <t>315820</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>556402</t>
+          <t>638242</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>548002</t>
+          <t>629693</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>561225</t>
+          <t>643666</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,6%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>289970</t>
+          <t>333805</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>289970</t>
+          <t>333805</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>289970</t>
+          <t>333805</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>279597</t>
+          <t>319011</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>279597</t>
+          <t>319011</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>279597</t>
+          <t>319011</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>569567</t>
+          <t>652816</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>569567</t>
+          <t>652816</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>569567</t>
+          <t>652816</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>16506</t>
+          <t>17131</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4334</t>
+          <t>10915</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>33907</t>
+          <t>25786</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>23111</t>
+          <t>24346</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16916</t>
+          <t>17653</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>31246</t>
+          <t>33061</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>39617</t>
+          <t>41477</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>17695</t>
+          <t>32202</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>59479</t>
+          <t>53642</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>7,46%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>536657</t>
+          <t>316148</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>519256</t>
+          <t>307493</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>548829</t>
+          <t>322364</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>336564</t>
+          <t>361740</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>328429</t>
+          <t>353025</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>342759</t>
+          <t>368433</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,31%</t>
+          <t>91,44%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>873221</t>
+          <t>677887</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>853359</t>
+          <t>665722</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>895143</t>
+          <t>687162</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>95,52%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>553163</t>
+          <t>333279</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>553163</t>
+          <t>333279</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>553163</t>
+          <t>333279</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>359675</t>
+          <t>386086</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>359675</t>
+          <t>386086</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>359675</t>
+          <t>386086</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>912838</t>
+          <t>719364</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>912838</t>
+          <t>719364</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>912838</t>
+          <t>719364</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>48299</t>
+          <t>51412</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>37993</t>
+          <t>40786</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>60780</t>
+          <t>64927</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>49319</t>
+          <t>55890</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>40594</t>
+          <t>45531</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>58659</t>
+          <t>66845</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>97618</t>
+          <t>107302</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>84468</t>
+          <t>93270</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>113283</t>
+          <t>123511</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>18,77%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>267829</t>
+          <t>289758</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>255348</t>
+          <t>276243</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>278135</t>
+          <t>300384</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>84,72%</t>
+          <t>84,93%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>80,77%</t>
+          <t>80,97%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>87,98%</t>
+          <t>88,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>233772</t>
+          <t>260969</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>224432</t>
+          <t>250014</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>242497</t>
+          <t>271328</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>82,58%</t>
+          <t>82,36%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>79,28%</t>
+          <t>78,9%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,66%</t>
+          <t>85,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>501601</t>
+          <t>550727</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>485936</t>
+          <t>534518</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>514751</t>
+          <t>564759</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>83,71%</t>
+          <t>83,69%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>81,09%</t>
+          <t>81,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>85,9%</t>
+          <t>85,83%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>316128</t>
+          <t>341170</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>316128</t>
+          <t>341170</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>316128</t>
+          <t>341170</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>283091</t>
+          <t>316859</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>283091</t>
+          <t>316859</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>283091</t>
+          <t>316859</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>599219</t>
+          <t>658029</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>599219</t>
+          <t>658029</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>599219</t>
+          <t>658029</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2440,32 +2440,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>50139</t>
+          <t>54876</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>41444</t>
+          <t>44729</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>60587</t>
+          <t>65555</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>30,66%</t>
+          <t>30,21%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>45374</t>
+          <t>50325</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11467</t>
+          <t>42198</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>113107</t>
+          <t>59782</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>30,57%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>25,63%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>36,31%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>95513</t>
+          <t>105201</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>37277</t>
+          <t>90664</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>157324</t>
+          <t>117659</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>30,83%</t>
         </is>
       </c>
     </row>
@@ -2553,32 +2553,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>147489</t>
+          <t>162091</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>137041</t>
+          <t>151412</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>156184</t>
+          <t>172238</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>74,63%</t>
+          <t>74,71%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>69,34%</t>
+          <t>69,79%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>79,03%</t>
+          <t>79,38%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>309807</t>
+          <t>114318</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>242074</t>
+          <t>104861</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>343714</t>
+          <t>122445</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>87,23%</t>
+          <t>69,43%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>68,15%</t>
+          <t>63,69%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>74,37%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>457296</t>
+          <t>276409</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>395485</t>
+          <t>263951</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>515532</t>
+          <t>290946</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>82,72%</t>
+          <t>72,43%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>71,54%</t>
+          <t>69,17%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
+          <t>76,24%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>197628</t>
+          <t>216967</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>197628</t>
+          <t>216967</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>197628</t>
+          <t>216967</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>355181</t>
+          <t>164643</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>355181</t>
+          <t>164643</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>355181</t>
+          <t>164643</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>552809</t>
+          <t>381610</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>552809</t>
+          <t>381610</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>552809</t>
+          <t>381610</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,32 +2783,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>41489</t>
+          <t>44818</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>34008</t>
+          <t>37396</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>49589</t>
+          <t>53576</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>37,61%</t>
+          <t>37,58%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>31,36%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>44,95%</t>
+          <t>44,92%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>47505</t>
+          <t>51840</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>40738</t>
+          <t>44229</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>55233</t>
+          <t>59608</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>43,39%</t>
+          <t>43,92%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>37,21%</t>
+          <t>37,47%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>50,45%</t>
+          <t>50,5%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>88994</t>
+          <t>96658</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>79336</t>
+          <t>85369</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>100176</t>
+          <t>108556</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>40,49%</t>
+          <t>40,73%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>36,1%</t>
+          <t>35,98%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>45,58%</t>
+          <t>45,75%</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>68823</t>
+          <t>74440</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>60723</t>
+          <t>65682</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>76304</t>
+          <t>81862</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>62,39%</t>
+          <t>62,42%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>55,05%</t>
+          <t>55,08%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>69,17%</t>
+          <t>68,64%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>61980</t>
+          <t>66194</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>54252</t>
+          <t>58426</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>68747</t>
+          <t>73805</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>56,61%</t>
+          <t>56,08%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>49,55%</t>
+          <t>49,5%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>62,79%</t>
+          <t>62,53%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>130803</t>
+          <t>140634</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>119621</t>
+          <t>128736</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>140461</t>
+          <t>151923</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>59,51%</t>
+          <t>59,27%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>54,42%</t>
+          <t>54,25%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>63,9%</t>
+          <t>64,02%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>110312</t>
+          <t>119258</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>110312</t>
+          <t>119258</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>110312</t>
+          <t>119258</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>109485</t>
+          <t>118034</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>109485</t>
+          <t>118034</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>109485</t>
+          <t>118034</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>219797</t>
+          <t>237292</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>219797</t>
+          <t>237292</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>219797</t>
+          <t>237292</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3126,32 +3126,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>174371</t>
+          <t>186425</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>111245</t>
+          <t>163464</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>214306</t>
+          <t>210543</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,32 +3161,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>183107</t>
+          <t>200639</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>115136</t>
+          <t>179746</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>216997</t>
+          <t>222327</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>357478</t>
+          <t>387064</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>259713</t>
+          <t>356631</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>414366</t>
+          <t>418249</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,76%</t>
         </is>
       </c>
     </row>
@@ -3239,32 +3239,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1584290</t>
+          <t>1472513</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1544355</t>
+          <t>1448395</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1647416</t>
+          <t>1495474</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>88,76%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>87,81%</t>
+          <t>87,31%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>90,15%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,32 +3274,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>1484199</t>
+          <t>1417339</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1450309</t>
+          <t>1395651</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1552170</t>
+          <t>1438232</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>87,6%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>86,99%</t>
+          <t>86,26%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>88,89%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>3068489</t>
+          <t>2889852</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3011601</t>
+          <t>2858667</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3166254</t>
+          <t>2920285</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>89,57%</t>
+          <t>88,19%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>87,24%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>89,12%</t>
         </is>
       </c>
     </row>
@@ -3352,17 +3352,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1758661</t>
+          <t>1658938</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1758661</t>
+          <t>1658938</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1758661</t>
+          <t>1658938</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1667306</t>
+          <t>1617978</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1667306</t>
+          <t>1617978</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1667306</t>
+          <t>1617978</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>3425967</t>
+          <t>3276916</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>3425967</t>
+          <t>3276916</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>3425967</t>
+          <t>3276916</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">

--- a/data/trans_orig/P41E_2023_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P41E_2023_R-Edad-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que en el último año sus relaciones sexuales han sido satisfactorias para ambas partes en 2023 (tasa de respuesta: 69,32%)</t>
+          <t>Población que en el último año declara que sus relaciones sexuales no han sido satisfactorias para ambas partes (bastante en desacuerdo/totalmente en desacuerdo) en 2023 (tasa de respuesta: 69,32%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
